--- a/campus-placement/qa/C-2-Tabular-Screens-CSV-Export.xlsx
+++ b/campus-placement/qa/C-2-Tabular-Screens-CSV-Export.xlsx
@@ -579,15 +579,11 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -655,15 +651,11 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -731,15 +723,11 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -807,15 +795,11 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -883,15 +867,11 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -959,15 +939,11 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1035,15 +1011,11 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1111,15 +1083,11 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1187,15 +1155,11 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1263,15 +1227,11 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1339,15 +1299,11 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1415,15 +1371,11 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1491,15 +1443,11 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1567,15 +1515,11 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1643,15 +1587,11 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1719,15 +1659,11 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1795,15 +1731,11 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1871,15 +1803,11 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1947,15 +1875,11 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2023,15 +1947,11 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2099,15 +2019,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2175,15 +2091,11 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2251,15 +2163,11 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2327,15 +2235,11 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2403,15 +2307,11 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2479,15 +2379,11 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2555,15 +2451,11 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
